--- a/June/21.06.2026/northwind.xlsx
+++ b/June/21.06.2026/northwind.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="14020" activeTab="5"/>
+    <workbookView windowWidth="17760" windowHeight="12380" firstSheet="6" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="categories" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,11 @@
     <sheet name="suppliers" sheetId="11" r:id="rId11"/>
     <sheet name="territories" sheetId="12" r:id="rId12"/>
     <sheet name="usstates" sheetId="13" r:id="rId13"/>
+    <sheet name="Sheet1" sheetId="14" r:id="rId14"/>
   </sheets>
+  <definedNames>
+    <definedName name="empinfo">employees!$A$1:$D$10</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7209" uniqueCount="1481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7231" uniqueCount="1499">
   <si>
     <t>categoryid</t>
   </si>
@@ -2321,15 +2325,6 @@
     <t>employeeid</t>
   </si>
   <si>
-    <t>lastname</t>
-  </si>
-  <si>
-    <t>firstname</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
     <t>titleofcourtesy</t>
   </si>
   <si>
@@ -2357,6 +2352,9 @@
     <t>photopath</t>
   </si>
   <si>
+    <t>manager name</t>
+  </si>
+  <si>
     <t>Fuller</t>
   </si>
   <si>
@@ -2912,6 +2910,9 @@
     <t>discontinued</t>
   </si>
   <si>
+    <t>product category name</t>
+  </si>
+  <si>
     <t>Chai</t>
   </si>
   <si>
@@ -4482,6 +4483,63 @@
   </si>
   <si>
     <t>Wyoming</t>
+  </si>
+  <si>
+    <t>Roll Number</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Hindi</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Math</t>
+  </si>
+  <si>
+    <t>Science</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Marks Obtained</t>
+  </si>
+  <si>
+    <t>Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John </t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>Leela</t>
+  </si>
+  <si>
+    <t>Amit</t>
+  </si>
+  <si>
+    <t>Mukesh</t>
+  </si>
+  <si>
+    <t>Suresh</t>
+  </si>
+  <si>
+    <t>Ajay</t>
+  </si>
+  <si>
+    <t>Ritesh</t>
+  </si>
+  <si>
+    <t>Santosh</t>
   </si>
 </sst>
 </file>
@@ -5569,13 +5627,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B1" t="s">
         <v>1123</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1124</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5583,10 +5641,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C2" t="s">
         <v>1111</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5594,10 +5652,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C3" t="s">
         <v>1113</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5605,10 +5663,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C4" t="s">
         <v>1115</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5616,10 +5674,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C5" t="s">
         <v>1117</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -5627,10 +5685,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C6" t="s">
         <v>1119</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5638,10 +5696,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C7" t="s">
         <v>1121</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1122</v>
       </c>
     </row>
   </sheetData>
@@ -5658,7 +5716,7 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B1" t="s">
         <v>22</v>
@@ -5691,7 +5749,7 @@
         <v>31</v>
       </c>
       <c r="L1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -5699,16 +5757,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C2" t="s">
         <v>1127</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>1128</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>1129</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1130</v>
       </c>
       <c r="F2" t="s">
         <v>62</v>
@@ -5717,13 +5775,13 @@
         <v>#N/A</v>
       </c>
       <c r="H2" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="I2" t="s">
         <v>64</v>
       </c>
       <c r="J2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="K2" t="e">
         <v>#N/A</v>
@@ -5737,37 +5795,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C3" t="s">
         <v>1133</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1134</v>
       </c>
       <c r="D3" t="s">
         <v>70</v>
       </c>
       <c r="E3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F3" t="s">
         <v>1135</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>1136</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>1137</v>
-      </c>
-      <c r="H3" t="s">
-        <v>1138</v>
       </c>
       <c r="I3" t="s">
         <v>295</v>
       </c>
       <c r="J3" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="K3" t="e">
         <v>#N/A</v>
       </c>
       <c r="L3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -5775,34 +5833,34 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C4" t="s">
         <v>1141</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1142</v>
       </c>
       <c r="D4" t="s">
         <v>35</v>
       </c>
       <c r="E4" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F4" t="s">
         <v>1143</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>1144</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>1145</v>
-      </c>
-      <c r="H4" t="s">
-        <v>1146</v>
       </c>
       <c r="I4" t="s">
         <v>295</v>
       </c>
       <c r="J4" t="s">
+        <v>1146</v>
+      </c>
+      <c r="K4" t="s">
         <v>1147</v>
-      </c>
-      <c r="K4" t="s">
-        <v>1148</v>
       </c>
       <c r="L4" t="e">
         <v>#N/A</v>
@@ -5813,31 +5871,31 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C5" t="s">
         <v>1149</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1150</v>
       </c>
       <c r="D5" t="s">
         <v>88</v>
       </c>
       <c r="E5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F5" t="s">
         <v>1151</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1152</v>
       </c>
       <c r="G5" t="e">
         <v>#N/A</v>
       </c>
       <c r="H5" t="s">
+        <v>1152</v>
+      </c>
+      <c r="I5" t="s">
         <v>1153</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>1154</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1155</v>
       </c>
       <c r="K5" t="e">
         <v>#N/A</v>
@@ -5851,31 +5909,31 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C6" t="s">
         <v>1156</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>1157</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>1158</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>1159</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>1160</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>1161</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1162</v>
       </c>
       <c r="I6" t="s">
         <v>101</v>
       </c>
       <c r="J6" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="K6" t="e">
         <v>#N/A</v>
@@ -5889,37 +5947,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C7" t="s">
         <v>1164</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>1165</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>1166</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>1167</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1168</v>
       </c>
       <c r="G7" t="e">
         <v>#N/A</v>
       </c>
       <c r="H7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="J7" t="s">
         <v>1169</v>
-      </c>
-      <c r="I7" t="s">
-        <v>1154</v>
-      </c>
-      <c r="J7" t="s">
-        <v>1170</v>
       </c>
       <c r="K7" t="e">
         <v>#N/A</v>
       </c>
       <c r="L7" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -5927,34 +5985,34 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C8" t="s">
         <v>1172</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1173</v>
       </c>
       <c r="D8" t="s">
         <v>88</v>
       </c>
       <c r="E8" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F8" t="s">
         <v>1174</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>1175</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>1176</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>1177</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>1178</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>1179</v>
-      </c>
-      <c r="K8" t="s">
-        <v>1180</v>
       </c>
       <c r="L8" t="e">
         <v>#N/A</v>
@@ -5965,31 +6023,31 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C9" t="s">
         <v>1181</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1182</v>
       </c>
       <c r="D9" t="s">
         <v>35</v>
       </c>
       <c r="E9" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F9" t="s">
         <v>1183</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1184</v>
       </c>
       <c r="G9" t="e">
         <v>#N/A</v>
       </c>
       <c r="H9" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="I9" t="s">
         <v>64</v>
       </c>
       <c r="J9" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="K9" t="e">
         <v>#N/A</v>
@@ -6003,34 +6061,34 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C10" t="s">
         <v>1187</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1188</v>
       </c>
       <c r="D10" t="s">
         <v>132</v>
       </c>
       <c r="E10" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F10" t="s">
         <v>1189</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1190</v>
       </c>
       <c r="G10" t="e">
         <v>#N/A</v>
       </c>
       <c r="H10" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="I10" t="s">
         <v>74</v>
       </c>
       <c r="J10" t="s">
+        <v>1191</v>
+      </c>
+      <c r="K10" t="s">
         <v>1192</v>
-      </c>
-      <c r="K10" t="s">
-        <v>1193</v>
       </c>
       <c r="L10" t="e">
         <v>#N/A</v>
@@ -6041,16 +6099,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C11" t="s">
         <v>1194</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1195</v>
       </c>
       <c r="D11" t="s">
         <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F11" t="s">
         <v>159</v>
@@ -6059,13 +6117,13 @@
         <v>#N/A</v>
       </c>
       <c r="H11" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="I11" t="s">
         <v>162</v>
       </c>
       <c r="J11" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="K11" t="e">
         <v>#N/A</v>
@@ -6079,16 +6137,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C12" t="s">
         <v>1199</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1200</v>
       </c>
       <c r="D12" t="s">
         <v>197</v>
       </c>
       <c r="E12" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="F12" t="s">
         <v>37</v>
@@ -6097,13 +6155,13 @@
         <v>#N/A</v>
       </c>
       <c r="H12" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="I12" t="s">
         <v>39</v>
       </c>
       <c r="J12" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K12" t="e">
         <v>#N/A</v>
@@ -6117,37 +6175,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C13" t="s">
         <v>1204</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>1205</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>1206</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>1207</v>
-      </c>
-      <c r="F13" t="s">
-        <v>1208</v>
       </c>
       <c r="G13" t="e">
         <v>#N/A</v>
       </c>
       <c r="H13" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="I13" t="s">
         <v>39</v>
       </c>
       <c r="J13" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="K13" t="e">
         <v>#N/A</v>
       </c>
       <c r="L13" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -6155,34 +6213,34 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C14" t="s">
         <v>1212</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>1213</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>1214</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>1215</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1216</v>
       </c>
       <c r="G14" t="e">
         <v>#N/A</v>
       </c>
       <c r="H14" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="I14" t="s">
         <v>39</v>
       </c>
       <c r="J14" t="s">
+        <v>1217</v>
+      </c>
+      <c r="K14" t="s">
         <v>1218</v>
-      </c>
-      <c r="K14" t="s">
-        <v>1219</v>
       </c>
       <c r="L14" t="e">
         <v>#N/A</v>
@@ -6193,37 +6251,37 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C15" t="s">
         <v>1220</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1221</v>
       </c>
       <c r="D15" t="s">
         <v>35</v>
       </c>
       <c r="E15" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F15" t="s">
         <v>1222</v>
-      </c>
-      <c r="F15" t="s">
-        <v>1223</v>
       </c>
       <c r="G15" t="e">
         <v>#N/A</v>
       </c>
       <c r="H15" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="I15" t="s">
         <v>254</v>
       </c>
       <c r="J15" t="s">
+        <v>1224</v>
+      </c>
+      <c r="K15" t="s">
         <v>1225</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>1226</v>
-      </c>
-      <c r="L15" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -6231,31 +6289,31 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C16" t="s">
         <v>1228</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1229</v>
       </c>
       <c r="D16" t="s">
         <v>88</v>
       </c>
       <c r="E16" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F16" t="s">
         <v>1230</v>
-      </c>
-      <c r="F16" t="s">
-        <v>1231</v>
       </c>
       <c r="G16" t="e">
         <v>#N/A</v>
       </c>
       <c r="H16" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="I16" t="s">
         <v>594</v>
       </c>
       <c r="J16" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="K16" t="e">
         <v>#N/A</v>
@@ -6269,31 +6327,31 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C17" t="s">
         <v>1234</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>1235</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>1236</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>1237</v>
-      </c>
-      <c r="F17" t="s">
-        <v>1238</v>
       </c>
       <c r="G17" t="s">
         <v>293</v>
       </c>
       <c r="H17" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="I17" t="s">
         <v>295</v>
       </c>
       <c r="J17" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="K17" t="e">
         <v>#N/A</v>
@@ -6307,31 +6365,31 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C18" t="s">
         <v>1240</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1241</v>
       </c>
       <c r="D18" t="s">
         <v>35</v>
       </c>
       <c r="E18" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F18" t="s">
         <v>1242</v>
-      </c>
-      <c r="F18" t="s">
-        <v>1243</v>
       </c>
       <c r="G18" t="e">
         <v>#N/A</v>
       </c>
       <c r="H18" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="I18" t="s">
         <v>74</v>
       </c>
       <c r="J18" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="K18" t="e">
         <v>#N/A</v>
@@ -6345,16 +6403,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C19" t="s">
         <v>1246</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1247</v>
       </c>
       <c r="D19" t="s">
         <v>197</v>
       </c>
       <c r="E19" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="F19" t="s">
         <v>499</v>
@@ -6363,16 +6421,16 @@
         <v>#N/A</v>
       </c>
       <c r="H19" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="I19" t="s">
         <v>92</v>
       </c>
       <c r="J19" t="s">
+        <v>1249</v>
+      </c>
+      <c r="K19" t="s">
         <v>1250</v>
-      </c>
-      <c r="K19" t="s">
-        <v>1251</v>
       </c>
       <c r="L19" t="e">
         <v>#N/A</v>
@@ -6383,34 +6441,34 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C20" t="s">
         <v>1252</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>1253</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>1254</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>1255</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>1256</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>1257</v>
-      </c>
-      <c r="H20" t="s">
-        <v>1258</v>
       </c>
       <c r="I20" t="s">
         <v>295</v>
       </c>
       <c r="J20" t="s">
+        <v>1258</v>
+      </c>
+      <c r="K20" t="s">
         <v>1259</v>
-      </c>
-      <c r="K20" t="s">
-        <v>1260</v>
       </c>
       <c r="L20" t="e">
         <v>#N/A</v>
@@ -6421,31 +6479,31 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C21" t="s">
         <v>1261</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1262</v>
       </c>
       <c r="D21" t="s">
         <v>45</v>
       </c>
       <c r="E21" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F21" t="s">
         <v>1263</v>
-      </c>
-      <c r="F21" t="s">
-        <v>1264</v>
       </c>
       <c r="G21" t="e">
         <v>#N/A</v>
       </c>
       <c r="H21" t="s">
+        <v>1264</v>
+      </c>
+      <c r="I21" t="s">
+        <v>1263</v>
+      </c>
+      <c r="J21" t="s">
         <v>1265</v>
-      </c>
-      <c r="I21" t="s">
-        <v>1264</v>
-      </c>
-      <c r="J21" t="s">
-        <v>1266</v>
       </c>
       <c r="K21" t="e">
         <v>#N/A</v>
@@ -6459,34 +6517,34 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C22" t="s">
         <v>1267</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1268</v>
       </c>
       <c r="D22" t="s">
         <v>197</v>
       </c>
       <c r="E22" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F22" t="s">
         <v>1269</v>
-      </c>
-      <c r="F22" t="s">
-        <v>1270</v>
       </c>
       <c r="G22" t="e">
         <v>#N/A</v>
       </c>
       <c r="H22" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="I22" t="s">
         <v>618</v>
       </c>
       <c r="J22" t="s">
+        <v>1271</v>
+      </c>
+      <c r="K22" t="s">
         <v>1272</v>
-      </c>
-      <c r="K22" t="s">
-        <v>1273</v>
       </c>
       <c r="L22" t="e">
         <v>#N/A</v>
@@ -6497,34 +6555,34 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C23" t="s">
         <v>1274</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1275</v>
       </c>
       <c r="D23" t="s">
         <v>115</v>
       </c>
       <c r="E23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F23" t="s">
         <v>1276</v>
-      </c>
-      <c r="F23" t="s">
-        <v>1277</v>
       </c>
       <c r="G23" t="e">
         <v>#N/A</v>
       </c>
       <c r="H23" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I23" t="s">
         <v>1278</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>1279</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>1280</v>
-      </c>
-      <c r="K23" t="s">
-        <v>1281</v>
       </c>
       <c r="L23" t="e">
         <v>#N/A</v>
@@ -6535,31 +6593,31 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C24" t="s">
         <v>1282</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>1283</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>1284</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>1285</v>
-      </c>
-      <c r="F24" t="s">
-        <v>1286</v>
       </c>
       <c r="G24" t="e">
         <v>#N/A</v>
       </c>
       <c r="H24" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="I24" t="s">
         <v>726</v>
       </c>
       <c r="J24" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="K24" t="e">
         <v>#N/A</v>
@@ -6573,37 +6631,37 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C25" t="s">
         <v>1289</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1290</v>
       </c>
       <c r="D25" t="s">
         <v>35</v>
       </c>
       <c r="E25" t="s">
+        <v>1290</v>
+      </c>
+      <c r="F25" t="s">
         <v>1291</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>1292</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>1293</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
+        <v>1177</v>
+      </c>
+      <c r="J25" t="s">
         <v>1294</v>
       </c>
-      <c r="I25" t="s">
-        <v>1178</v>
-      </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>1295</v>
       </c>
-      <c r="K25" t="s">
+      <c r="L25" t="s">
         <v>1296</v>
-      </c>
-      <c r="L25" t="s">
-        <v>1297</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -6611,16 +6669,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C26" t="s">
         <v>1298</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1299</v>
       </c>
       <c r="D26" t="s">
         <v>88</v>
       </c>
       <c r="E26" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="F26" t="s">
         <v>453</v>
@@ -6635,7 +6693,7 @@
         <v>120</v>
       </c>
       <c r="J26" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="K26" t="e">
         <v>#N/A</v>
@@ -6649,34 +6707,34 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C27" t="s">
         <v>1302</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1303</v>
       </c>
       <c r="D27" t="s">
         <v>70</v>
       </c>
       <c r="E27" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F27" t="s">
         <v>1304</v>
-      </c>
-      <c r="F27" t="s">
-        <v>1305</v>
       </c>
       <c r="G27" t="e">
         <v>#N/A</v>
       </c>
       <c r="H27" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="I27" t="s">
         <v>254</v>
       </c>
       <c r="J27" t="s">
+        <v>1306</v>
+      </c>
+      <c r="K27" t="s">
         <v>1307</v>
-      </c>
-      <c r="K27" t="s">
-        <v>1308</v>
       </c>
       <c r="L27" t="e">
         <v>#N/A</v>
@@ -6687,31 +6745,31 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C28" t="s">
         <v>1309</v>
-      </c>
-      <c r="C28" t="s">
-        <v>1310</v>
       </c>
       <c r="D28" t="s">
         <v>197</v>
       </c>
       <c r="E28" t="s">
+        <v>1310</v>
+      </c>
+      <c r="F28" t="s">
         <v>1311</v>
-      </c>
-      <c r="F28" t="s">
-        <v>1312</v>
       </c>
       <c r="G28" t="e">
         <v>#N/A</v>
       </c>
       <c r="H28" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="I28" t="s">
         <v>92</v>
       </c>
       <c r="J28" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="K28" t="e">
         <v>#N/A</v>
@@ -6725,34 +6783,34 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C29" t="s">
         <v>1315</v>
-      </c>
-      <c r="C29" t="s">
-        <v>1316</v>
       </c>
       <c r="D29" t="s">
         <v>35</v>
       </c>
       <c r="E29" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F29" t="s">
         <v>1317</v>
-      </c>
-      <c r="F29" t="s">
-        <v>1318</v>
       </c>
       <c r="G29" t="e">
         <v>#N/A</v>
       </c>
       <c r="H29" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="I29" t="s">
         <v>92</v>
       </c>
       <c r="J29" t="s">
+        <v>1319</v>
+      </c>
+      <c r="K29" t="s">
         <v>1320</v>
-      </c>
-      <c r="K29" t="s">
-        <v>1321</v>
       </c>
       <c r="L29" t="e">
         <v>#N/A</v>
@@ -6763,34 +6821,34 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C30" t="s">
         <v>1322</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1323</v>
       </c>
       <c r="D30" t="s">
         <v>115</v>
       </c>
       <c r="E30" t="s">
+        <v>1323</v>
+      </c>
+      <c r="F30" t="s">
         <v>1324</v>
-      </c>
-      <c r="F30" t="s">
-        <v>1325</v>
       </c>
       <c r="G30" t="s">
         <v>454</v>
       </c>
       <c r="H30" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="I30" t="s">
         <v>120</v>
       </c>
       <c r="J30" t="s">
+        <v>1326</v>
+      </c>
+      <c r="K30" t="s">
         <v>1327</v>
-      </c>
-      <c r="K30" t="s">
-        <v>1328</v>
       </c>
       <c r="L30" t="e">
         <v>#N/A</v>
@@ -6810,21 +6868,21 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B1" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B2" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -6832,10 +6890,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B3" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -6843,10 +6901,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B4" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -6854,10 +6912,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B5" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6865,10 +6923,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B6" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -6876,10 +6934,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B7" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -6887,10 +6945,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B8" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -6898,10 +6956,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B9" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -6909,10 +6967,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B10" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -6920,10 +6978,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B11" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -6931,10 +6989,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B12" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -6942,10 +7000,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B13" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -6953,10 +7011,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B14" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -6964,10 +7022,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B15" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -6975,10 +7033,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B16" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -6986,10 +7044,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B17" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -6997,10 +7055,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B18" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -7008,10 +7066,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B19" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -7019,10 +7077,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B20" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -7030,10 +7088,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B21" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -7041,10 +7099,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B22" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -7052,10 +7110,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B23" t="s">
         <v>1349</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1350</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -7063,10 +7121,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B24" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="C24">
         <v>4</v>
@@ -7074,10 +7132,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B25" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C25">
         <v>4</v>
@@ -7085,10 +7143,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B26" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C26">
         <v>4</v>
@@ -7096,10 +7154,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B27" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="C27">
         <v>4</v>
@@ -7107,10 +7165,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B28" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -7118,10 +7176,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B29" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -7129,10 +7187,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B30" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -7140,10 +7198,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B31" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -7151,10 +7209,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B32" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="C32">
         <v>3</v>
@@ -7162,10 +7220,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B33" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -7173,10 +7231,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B34" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="C34">
         <v>3</v>
@@ -7184,10 +7242,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B35" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C35">
         <v>3</v>
@@ -7195,10 +7253,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B36" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="C36">
         <v>3</v>
@@ -7206,10 +7264,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B37" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -7217,10 +7275,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B38" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -7228,10 +7286,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B39" t="s">
         <v>1366</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1367</v>
       </c>
       <c r="C39">
         <v>4</v>
@@ -7239,10 +7297,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B40" t="s">
         <v>1368</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1369</v>
       </c>
       <c r="C40">
         <v>4</v>
@@ -7250,10 +7308,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B41" t="s">
         <v>1370</v>
-      </c>
-      <c r="B41" t="s">
-        <v>1371</v>
       </c>
       <c r="C41">
         <v>4</v>
@@ -7261,10 +7319,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B42" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -7272,10 +7330,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B43" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -7283,10 +7341,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B44" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -7294,10 +7352,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B45" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -7305,10 +7363,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B46" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="C46">
         <v>2</v>
@@ -7316,10 +7374,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B47" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="C47">
         <v>2</v>
@@ -7327,7 +7385,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B48" t="s">
         <v>402</v>
@@ -7338,10 +7396,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B49" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -7349,10 +7407,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B50" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -7360,10 +7418,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B51" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -7371,10 +7429,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B52" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="C52">
         <v>2</v>
@@ -7382,10 +7440,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B53" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -7393,7 +7451,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B54" t="s">
         <v>739</v>
@@ -7416,16 +7474,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B1" t="s">
         <v>1382</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1383</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1384</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1385</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -7433,13 +7491,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C2" t="s">
         <v>1386</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>1387</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -7447,13 +7505,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="C3" t="s">
         <v>483</v>
       </c>
       <c r="D3" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -7461,13 +7519,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C4" t="s">
         <v>1391</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>1392</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1393</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7475,13 +7533,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C5" t="s">
         <v>1394</v>
       </c>
-      <c r="C5" t="s">
-        <v>1395</v>
-      </c>
       <c r="D5" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7489,13 +7547,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C6" t="s">
         <v>403</v>
       </c>
       <c r="D6" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7503,13 +7561,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C7" t="s">
         <v>1397</v>
       </c>
-      <c r="C7" t="s">
-        <v>1398</v>
-      </c>
       <c r="D7" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7517,13 +7575,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C8" t="s">
         <v>1399</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>1400</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1401</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7531,13 +7589,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C9" t="s">
         <v>1402</v>
       </c>
-      <c r="C9" t="s">
-        <v>1403</v>
-      </c>
       <c r="D9" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7545,13 +7603,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C10" t="s">
         <v>1404</v>
       </c>
-      <c r="C10" t="s">
-        <v>1405</v>
-      </c>
       <c r="D10" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -7559,13 +7617,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C11" t="s">
         <v>1406</v>
       </c>
-      <c r="C11" t="s">
-        <v>1407</v>
-      </c>
       <c r="D11" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -7573,13 +7631,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C12" t="s">
         <v>1408</v>
       </c>
-      <c r="C12" t="s">
-        <v>1409</v>
-      </c>
       <c r="D12" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -7587,13 +7645,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C13" t="s">
         <v>1410</v>
       </c>
-      <c r="C13" t="s">
-        <v>1411</v>
-      </c>
       <c r="D13" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -7601,13 +7659,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="C14" t="s">
         <v>602</v>
       </c>
       <c r="D14" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -7615,13 +7673,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C15" t="s">
         <v>1414</v>
       </c>
-      <c r="C15" t="s">
-        <v>1415</v>
-      </c>
       <c r="D15" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -7629,13 +7687,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C16" t="s">
         <v>1416</v>
       </c>
-      <c r="C16" t="s">
-        <v>1417</v>
-      </c>
       <c r="D16" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -7643,13 +7701,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C17" t="s">
         <v>1418</v>
       </c>
-      <c r="C17" t="s">
-        <v>1419</v>
-      </c>
       <c r="D17" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -7657,13 +7715,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C18" t="s">
         <v>1420</v>
       </c>
-      <c r="C18" t="s">
-        <v>1421</v>
-      </c>
       <c r="D18" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -7671,13 +7729,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C19" t="s">
         <v>1422</v>
       </c>
-      <c r="C19" t="s">
-        <v>1423</v>
-      </c>
       <c r="D19" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -7685,13 +7743,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="C20" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D20" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -7699,13 +7757,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C21" t="s">
         <v>1425</v>
       </c>
-      <c r="C21" t="s">
-        <v>1426</v>
-      </c>
       <c r="D21" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -7713,13 +7771,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C22" t="s">
         <v>1427</v>
       </c>
-      <c r="C22" t="s">
-        <v>1428</v>
-      </c>
       <c r="D22" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -7727,13 +7785,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="C23" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D23" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -7741,13 +7799,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="C24" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D24" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -7755,13 +7813,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C25" t="s">
         <v>1431</v>
       </c>
-      <c r="C25" t="s">
-        <v>1432</v>
-      </c>
       <c r="D25" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -7769,13 +7827,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C26" t="s">
         <v>1433</v>
       </c>
-      <c r="C26" t="s">
-        <v>1434</v>
-      </c>
       <c r="D26" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -7783,13 +7841,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C27" t="s">
         <v>1435</v>
       </c>
-      <c r="C27" t="s">
-        <v>1436</v>
-      </c>
       <c r="D27" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -7797,13 +7855,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="C28" t="s">
         <v>656</v>
       </c>
       <c r="D28" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -7811,13 +7869,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C29" t="s">
         <v>1438</v>
       </c>
-      <c r="C29" t="s">
-        <v>1439</v>
-      </c>
       <c r="D29" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -7825,13 +7883,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C30" t="s">
         <v>1440</v>
       </c>
-      <c r="C30" t="s">
-        <v>1441</v>
-      </c>
       <c r="D30" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -7839,13 +7897,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C31" t="s">
         <v>1442</v>
       </c>
-      <c r="C31" t="s">
-        <v>1443</v>
-      </c>
       <c r="D31" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -7853,13 +7911,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C32" t="s">
         <v>1444</v>
       </c>
-      <c r="C32" t="s">
-        <v>1445</v>
-      </c>
       <c r="D32" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -7867,13 +7925,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="C33" t="s">
         <v>556</v>
       </c>
       <c r="D33" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -7881,13 +7939,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C34" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="D34" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -7895,13 +7953,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C35" t="s">
         <v>1448</v>
       </c>
-      <c r="C35" t="s">
-        <v>1449</v>
-      </c>
       <c r="D35" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -7909,13 +7967,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C36" t="s">
         <v>1450</v>
       </c>
-      <c r="C36" t="s">
-        <v>1451</v>
-      </c>
       <c r="D36" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -7923,13 +7981,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C37" t="s">
         <v>1452</v>
       </c>
-      <c r="C37" t="s">
-        <v>1453</v>
-      </c>
       <c r="D37" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -7937,13 +7995,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C38" t="s">
         <v>1454</v>
       </c>
-      <c r="C38" t="s">
-        <v>1455</v>
-      </c>
       <c r="D38" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -7951,13 +8009,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="C39" t="s">
         <v>293</v>
       </c>
       <c r="D39" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -7965,13 +8023,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C40" t="s">
         <v>1457</v>
       </c>
-      <c r="C40" t="s">
-        <v>1458</v>
-      </c>
       <c r="D40" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -7979,13 +8037,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C41" t="s">
         <v>1459</v>
       </c>
-      <c r="C41" t="s">
-        <v>1460</v>
-      </c>
       <c r="D41" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -7993,13 +8051,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C42" t="s">
         <v>1461</v>
       </c>
-      <c r="C42" t="s">
-        <v>1462</v>
-      </c>
       <c r="D42" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -8007,13 +8065,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C43" t="s">
         <v>1463</v>
       </c>
-      <c r="C43" t="s">
-        <v>1464</v>
-      </c>
       <c r="D43" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -8021,13 +8079,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C44" t="s">
         <v>1465</v>
       </c>
-      <c r="C44" t="s">
-        <v>1466</v>
-      </c>
       <c r="D44" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -8035,13 +8093,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C45" t="s">
         <v>1467</v>
       </c>
-      <c r="C45" t="s">
-        <v>1468</v>
-      </c>
       <c r="D45" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -8049,13 +8107,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C46" t="s">
         <v>1469</v>
       </c>
-      <c r="C46" t="s">
-        <v>1470</v>
-      </c>
       <c r="D46" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -8063,13 +8121,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C47" t="s">
         <v>1471</v>
       </c>
-      <c r="C47" t="s">
-        <v>1472</v>
-      </c>
       <c r="D47" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -8077,13 +8135,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C48" t="s">
         <v>1473</v>
       </c>
-      <c r="C48" t="s">
-        <v>1474</v>
-      </c>
       <c r="D48" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -8091,13 +8149,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="C49" t="s">
         <v>386</v>
       </c>
       <c r="D49" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -8105,13 +8163,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C50" t="s">
         <v>1476</v>
       </c>
-      <c r="C50" t="s">
-        <v>1477</v>
-      </c>
       <c r="D50" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -8119,13 +8177,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C51" t="s">
         <v>1478</v>
       </c>
-      <c r="C51" t="s">
-        <v>1479</v>
-      </c>
       <c r="D51" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -8133,17 +8191,372 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="C52" t="s">
         <v>633</v>
       </c>
       <c r="D52" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="1" max="1" width="11.71875" customWidth="1"/>
+    <col min="8" max="8" width="13.7890625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1486</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C2">
+        <v>56</v>
+      </c>
+      <c r="D2">
+        <v>56</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+      <c r="F2">
+        <v>78</v>
+      </c>
+      <c r="G2">
+        <v>55</v>
+      </c>
+      <c r="H2">
+        <f>SUM(C2:G2)</f>
+        <v>310</v>
+      </c>
+      <c r="I2">
+        <f>H2/500*100</f>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C3">
+        <v>76</v>
+      </c>
+      <c r="D3">
+        <v>78</v>
+      </c>
+      <c r="E3">
+        <v>78</v>
+      </c>
+      <c r="F3">
+        <v>87</v>
+      </c>
+      <c r="G3">
+        <v>55</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H11" si="0">SUM(C3:G3)</f>
+        <v>374</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I11" si="1">H3/500*100</f>
+        <v>74.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>103</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C4">
+        <v>56</v>
+      </c>
+      <c r="D4">
+        <v>56</v>
+      </c>
+      <c r="E4">
+        <v>45</v>
+      </c>
+      <c r="F4">
+        <v>78</v>
+      </c>
+      <c r="G4">
+        <v>45</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>280</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>104</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C5">
+        <v>45</v>
+      </c>
+      <c r="D5">
+        <v>78</v>
+      </c>
+      <c r="E5">
+        <v>98</v>
+      </c>
+      <c r="F5">
+        <v>89</v>
+      </c>
+      <c r="G5">
+        <v>98</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>408</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="1"/>
+        <v>81.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>105</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C6">
+        <v>65</v>
+      </c>
+      <c r="D6">
+        <v>34</v>
+      </c>
+      <c r="E6">
+        <v>78</v>
+      </c>
+      <c r="F6">
+        <v>98</v>
+      </c>
+      <c r="G6">
+        <v>54</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>329</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>65.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>106</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C7">
+        <v>45</v>
+      </c>
+      <c r="D7">
+        <v>65</v>
+      </c>
+      <c r="E7">
+        <v>98</v>
+      </c>
+      <c r="F7">
+        <v>90</v>
+      </c>
+      <c r="G7">
+        <v>67</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>365</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>107</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C8">
+        <v>65</v>
+      </c>
+      <c r="D8">
+        <v>45</v>
+      </c>
+      <c r="E8">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>98</v>
+      </c>
+      <c r="G8">
+        <v>56</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>309</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="1"/>
+        <v>61.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>108</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C9">
+        <v>45</v>
+      </c>
+      <c r="D9">
+        <v>65</v>
+      </c>
+      <c r="E9">
+        <v>64</v>
+      </c>
+      <c r="F9">
+        <v>88</v>
+      </c>
+      <c r="G9">
+        <v>45</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>307</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="1"/>
+        <v>61.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>109</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C10">
+        <v>78</v>
+      </c>
+      <c r="D10">
+        <v>78</v>
+      </c>
+      <c r="E10">
+        <v>34</v>
+      </c>
+      <c r="F10">
+        <v>87</v>
+      </c>
+      <c r="G10">
+        <v>65</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>342</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>68.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>110</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C11">
+        <v>56</v>
+      </c>
+      <c r="D11">
+        <v>34</v>
+      </c>
+      <c r="E11">
+        <v>34</v>
+      </c>
+      <c r="F11">
+        <v>78</v>
+      </c>
+      <c r="G11">
+        <v>56</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>258</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="1"/>
+        <v>51.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -11383,7 +11796,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="16.8"/>
   <cols>
     <col min="6" max="6" width="9.5" customWidth="1"/>
@@ -11391,27 +11804,27 @@
     <col min="13" max="13" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>759</v>
       </c>
       <c r="B1" t="s">
+        <v>759</v>
+      </c>
+      <c r="C1" t="s">
+        <v>759</v>
+      </c>
+      <c r="D1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E1" t="s">
         <v>760</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>761</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>762</v>
-      </c>
-      <c r="E1" t="s">
-        <v>763</v>
-      </c>
-      <c r="F1" t="s">
-        <v>764</v>
-      </c>
-      <c r="G1" t="s">
-        <v>765</v>
       </c>
       <c r="H1" t="s">
         <v>25</v>
@@ -11429,39 +11842,42 @@
         <v>29</v>
       </c>
       <c r="M1" t="s">
+        <v>763</v>
+      </c>
+      <c r="N1" t="s">
+        <v>764</v>
+      </c>
+      <c r="O1" t="s">
+        <v>765</v>
+      </c>
+      <c r="P1" t="s">
         <v>766</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>767</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>768</v>
       </c>
-      <c r="P1" t="s">
+      <c r="V1" t="s">
         <v>769</v>
       </c>
-      <c r="Q1" t="s">
-        <v>770</v>
-      </c>
-      <c r="R1" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2">
         <v>2</v>
       </c>
       <c r="B2" t="s">
+        <v>770</v>
+      </c>
+      <c r="C2" t="s">
+        <v>771</v>
+      </c>
+      <c r="D2" t="s">
         <v>772</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>773</v>
-      </c>
-      <c r="D2" t="s">
-        <v>774</v>
-      </c>
-      <c r="E2" t="s">
-        <v>775</v>
       </c>
       <c r="F2" s="1">
         <v>19043</v>
@@ -11470,54 +11886,58 @@
         <v>33830</v>
       </c>
       <c r="H2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="I2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="J2" t="s">
         <v>386</v>
       </c>
       <c r="K2" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="L2" t="s">
         <v>295</v>
       </c>
       <c r="M2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="N2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="O2" t="s">
         <v>6</v>
       </c>
       <c r="P2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="Q2" t="e">
         <v>#N/A</v>
       </c>
       <c r="R2" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
+        <v>780</v>
+      </c>
+      <c r="V2" t="e">
+        <f>VLOOKUP(Q2,empinfo,3,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C3" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D3" t="s">
         <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="F3" s="1">
         <v>17875</v>
@@ -11526,7 +11946,7 @@
         <v>33725</v>
       </c>
       <c r="H3" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="I3" t="s">
         <v>739</v>
@@ -11535,45 +11955,49 @@
         <v>386</v>
       </c>
       <c r="K3" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="L3" t="s">
         <v>295</v>
       </c>
       <c r="M3" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="N3" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="O3" t="s">
         <v>6</v>
       </c>
       <c r="P3" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="Q3">
         <v>2</v>
       </c>
       <c r="R3" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
+        <v>789</v>
+      </c>
+      <c r="V3" t="str">
+        <f>VLOOKUP(Q3,empinfo,3,0)</f>
+        <v>Andrew</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C4" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D4" t="s">
         <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="F4" s="1">
         <v>23253</v>
@@ -11582,7 +12006,7 @@
         <v>33695</v>
       </c>
       <c r="H4" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="I4" t="s">
         <v>684</v>
@@ -11591,45 +12015,49 @@
         <v>386</v>
       </c>
       <c r="K4" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="L4" t="s">
         <v>295</v>
       </c>
       <c r="M4" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="N4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="O4" t="s">
         <v>6</v>
       </c>
       <c r="P4" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="Q4">
         <v>2</v>
       </c>
       <c r="R4" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+        <v>797</v>
+      </c>
+      <c r="V4" t="str">
+        <f>VLOOKUP(Q4,empinfo,3,0)</f>
+        <v>Andrew</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C5" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D5" t="s">
         <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F5" s="1">
         <v>13777</v>
@@ -11638,54 +12066,58 @@
         <v>34092</v>
       </c>
       <c r="H5" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="I5" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="J5" t="s">
         <v>386</v>
       </c>
       <c r="K5" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="L5" t="s">
         <v>295</v>
       </c>
       <c r="M5" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="N5" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="O5" t="s">
         <v>6</v>
       </c>
       <c r="P5" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="Q5">
         <v>2</v>
       </c>
       <c r="R5" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+        <v>807</v>
+      </c>
+      <c r="V5" t="str">
+        <f>VLOOKUP(Q5,empinfo,3,0)</f>
+        <v>Andrew</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C6" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="D6" t="s">
         <v>197</v>
       </c>
       <c r="E6" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="F6" s="1">
         <v>20152</v>
@@ -11694,7 +12126,7 @@
         <v>34259</v>
       </c>
       <c r="H6" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="I6" t="s">
         <v>62</v>
@@ -11703,45 +12135,49 @@
         <v>#N/A</v>
       </c>
       <c r="K6" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="L6" t="s">
         <v>64</v>
       </c>
       <c r="M6" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="N6" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="O6" t="s">
         <v>6</v>
       </c>
       <c r="P6" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="Q6">
         <v>2</v>
       </c>
       <c r="R6" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+        <v>816</v>
+      </c>
+      <c r="V6" t="str">
+        <f>VLOOKUP(Q6,empinfo,3,0)</f>
+        <v>Andrew</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C7" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="D7" t="s">
         <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="F7" s="1">
         <v>23194</v>
@@ -11750,7 +12186,7 @@
         <v>34259</v>
       </c>
       <c r="H7" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="I7" t="s">
         <v>62</v>
@@ -11759,45 +12195,49 @@
         <v>#N/A</v>
       </c>
       <c r="K7" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="L7" t="s">
         <v>64</v>
       </c>
       <c r="M7" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="N7" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="O7" t="s">
         <v>6</v>
       </c>
       <c r="P7" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="Q7">
         <v>5</v>
       </c>
       <c r="R7" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
+        <v>789</v>
+      </c>
+      <c r="V7" t="str">
+        <f>VLOOKUP(Q7,empinfo,3,0)</f>
+        <v>Steven</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C8" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D8" t="s">
         <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="F8" s="1">
         <v>22065</v>
@@ -11806,7 +12246,7 @@
         <v>34336</v>
       </c>
       <c r="H8" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="I8" t="s">
         <v>62</v>
@@ -11815,45 +12255,49 @@
         <v>#N/A</v>
       </c>
       <c r="K8" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="L8" t="s">
         <v>64</v>
       </c>
       <c r="M8" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="N8" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="O8" t="s">
         <v>6</v>
       </c>
       <c r="P8" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="Q8">
         <v>5</v>
       </c>
       <c r="R8" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
+        <v>789</v>
+      </c>
+      <c r="V8" t="str">
+        <f>VLOOKUP(Q8,empinfo,3,0)</f>
+        <v>Steven</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>831</v>
+      </c>
+      <c r="C9" t="s">
+        <v>832</v>
+      </c>
+      <c r="D9" t="s">
         <v>833</v>
       </c>
-      <c r="C9" t="s">
-        <v>834</v>
-      </c>
-      <c r="D9" t="s">
-        <v>835</v>
-      </c>
       <c r="E9" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="F9" s="1">
         <v>21194</v>
@@ -11862,7 +12306,7 @@
         <v>34398</v>
       </c>
       <c r="H9" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="I9" t="s">
         <v>739</v>
@@ -11871,45 +12315,49 @@
         <v>386</v>
       </c>
       <c r="K9" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="L9" t="s">
         <v>295</v>
       </c>
       <c r="M9" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="N9" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="O9" t="s">
         <v>6</v>
       </c>
       <c r="P9" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="Q9">
         <v>2</v>
       </c>
       <c r="R9" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
+        <v>789</v>
+      </c>
+      <c r="V9" t="str">
+        <f>VLOOKUP(Q9,empinfo,3,0)</f>
+        <v>Andrew</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C10" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="D10" t="s">
         <v>35</v>
       </c>
       <c r="E10" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="F10" s="1">
         <v>24134</v>
@@ -11918,7 +12366,7 @@
         <v>34653</v>
       </c>
       <c r="H10" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="I10" t="s">
         <v>62</v>
@@ -11927,28 +12375,32 @@
         <v>#N/A</v>
       </c>
       <c r="K10" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="L10" t="s">
         <v>64</v>
       </c>
       <c r="M10" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="N10" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="O10" t="s">
         <v>6</v>
       </c>
       <c r="P10" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="Q10">
         <v>5</v>
       </c>
       <c r="R10" t="s">
-        <v>791</v>
+        <v>789</v>
+      </c>
+      <c r="V10" t="str">
+        <f>VLOOKUP(Q10,empinfo,3,0)</f>
+        <v>Steven</v>
       </c>
     </row>
     <row r="18" spans="6:6">
@@ -11980,7 +12432,7 @@
         <v>759</v>
       </c>
       <c r="B1" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -11988,7 +12440,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -11996,7 +12448,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -12004,7 +12456,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -12012,7 +12464,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -12020,7 +12472,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -12028,7 +12480,7 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -12036,7 +12488,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -12044,7 +12496,7 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -12052,7 +12504,7 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -12060,7 +12512,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -12068,7 +12520,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -12076,7 +12528,7 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -12084,7 +12536,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -12092,7 +12544,7 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -12100,7 +12552,7 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -12108,7 +12560,7 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -12116,7 +12568,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -12124,7 +12576,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -12132,7 +12584,7 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -12140,7 +12592,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -12148,7 +12600,7 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -12156,7 +12608,7 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -12164,7 +12616,7 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -12172,7 +12624,7 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -12180,7 +12632,7 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -12188,7 +12640,7 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -12196,7 +12648,7 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -12204,7 +12656,7 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -12212,7 +12664,7 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -12220,7 +12672,7 @@
         <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -12228,7 +12680,7 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -12236,7 +12688,7 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -12244,7 +12696,7 @@
         <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -12252,7 +12704,7 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -12260,7 +12712,7 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -12268,7 +12720,7 @@
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -12276,7 +12728,7 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -12284,7 +12736,7 @@
         <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -12292,7 +12744,7 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -12300,7 +12752,7 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -12308,7 +12760,7 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -12316,7 +12768,7 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -12324,7 +12776,7 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -12332,7 +12784,7 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -12340,7 +12792,7 @@
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -12348,7 +12800,7 @@
         <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -12356,7 +12808,7 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -12364,7 +12816,7 @@
         <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -12372,7 +12824,7 @@
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
   </sheetData>
@@ -12390,30 +12842,30 @@
     <col min="6" max="6" width="12.6875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1" t="s">
+        <v>896</v>
+      </c>
+      <c r="C1" t="s">
         <v>897</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>898</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>899</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>900</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>901</v>
       </c>
-      <c r="F1" t="s">
-        <v>902</v>
-      </c>
-      <c r="G1" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>10248</v>
       </c>
@@ -12437,8 +12889,12 @@
         <f>C2*$H$2176</f>
         <v>1.4</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2">
+        <f>ABS(C2*H2176)</f>
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>10248</v>
       </c>
@@ -12463,7 +12919,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>10248</v>
       </c>
@@ -12488,7 +12944,7 @@
         <v>3.48</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>10249</v>
       </c>
@@ -12513,7 +12969,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>10249</v>
       </c>
@@ -12538,7 +12994,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>10250</v>
       </c>
@@ -12563,7 +13019,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>10250</v>
       </c>
@@ -12588,7 +13044,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>10250</v>
       </c>
@@ -12613,7 +13069,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>10251</v>
       </c>
@@ -12638,7 +13094,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>10251</v>
       </c>
@@ -12663,7 +13119,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>10251</v>
       </c>
@@ -12688,7 +13144,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>10252</v>
       </c>
@@ -12713,7 +13169,7 @@
         <v>6.48</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>10252</v>
       </c>
@@ -12738,7 +13194,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>10252</v>
       </c>
@@ -12763,7 +13219,7 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>10253</v>
       </c>
@@ -66290,7 +66746,7 @@
     </row>
     <row r="2157" spans="1:11">
       <c r="F2157" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="2158" spans="1:11">
@@ -66299,14 +66755,13 @@
         <v>628.519067285383</v>
       </c>
       <c r="K2158" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="2159" spans="1:11">
       <c r="F2159" t="s">
-        <v>906</v>
-      </c>
-      <c r="G2159"/>
+        <v>904</v>
+      </c>
       <c r="K2159">
         <v>23</v>
       </c>
@@ -66325,15 +66780,14 @@
     </row>
     <row r="2161" spans="2:11">
       <c r="B2161" t="s">
+        <v>905</v>
+      </c>
+      <c r="C2161" t="s">
+        <v>906</v>
+      </c>
+      <c r="F2161" t="s">
         <v>907</v>
       </c>
-      <c r="C2161" t="s">
-        <v>908</v>
-      </c>
-      <c r="F2161" t="s">
-        <v>909</v>
-      </c>
-      <c r="G2161"/>
       <c r="K2161">
         <v>45</v>
       </c>
@@ -66360,9 +66814,8 @@
         <v>120</v>
       </c>
       <c r="F2163" t="s">
-        <v>910</v>
-      </c>
-      <c r="G2163"/>
+        <v>908</v>
+      </c>
       <c r="K2163">
         <v>32</v>
       </c>
@@ -66392,11 +66845,10 @@
         <v>423</v>
       </c>
       <c r="F2165" t="s">
-        <v>911</v>
-      </c>
-      <c r="G2165"/>
+        <v>909</v>
+      </c>
       <c r="K2165" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="2166" spans="2:11">
@@ -66418,11 +66870,10 @@
     </row>
     <row r="2167" spans="2:11">
       <c r="F2167" t="s">
-        <v>913</v>
-      </c>
-      <c r="G2167"/>
+        <v>911</v>
+      </c>
       <c r="K2167" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="2168" spans="2:11">
@@ -66437,7 +66888,7 @@
     </row>
     <row r="2169" spans="2:11">
       <c r="F2169" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="2170" spans="2:11">
@@ -66448,7 +66899,7 @@
     </row>
     <row r="2171" spans="2:11">
       <c r="F2171" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="2172" spans="2:11">
@@ -66459,7 +66910,7 @@
     </row>
     <row r="2173" spans="2:11">
       <c r="F2173" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="2174" spans="2:11">
@@ -66470,7 +66921,7 @@
     </row>
     <row r="2176" spans="2:11">
       <c r="F2176" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="H2176" s="2">
         <v>0.1</v>
@@ -66493,7 +66944,7 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B1" t="s">
         <v>21</v>
@@ -66502,40 +66953,40 @@
         <v>759</v>
       </c>
       <c r="D1" t="s">
+        <v>917</v>
+      </c>
+      <c r="E1" t="s">
+        <v>918</v>
+      </c>
+      <c r="F1" t="s">
         <v>919</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>920</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>921</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>922</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>923</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>924</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>925</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>926</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>927</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>928</v>
-      </c>
-      <c r="N1" t="s">
-        <v>929</v>
-      </c>
-      <c r="O1" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -66730,7 +67181,7 @@
         <v>False</v>
       </c>
       <c r="P5" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -66833,7 +67284,7 @@
         <v>True</v>
       </c>
       <c r="P7" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -66865,7 +67316,7 @@
         <v>147</v>
       </c>
       <c r="J8" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="K8" t="s">
         <v>150</v>
@@ -66917,7 +67368,7 @@
         <v>575</v>
       </c>
       <c r="J9" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="K9" t="s">
         <v>578</v>
@@ -66926,7 +67377,7 @@
         <v>#N/A</v>
       </c>
       <c r="M9" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="N9" t="s">
         <v>152</v>
@@ -66936,7 +67387,7 @@
         <v>True</v>
       </c>
       <c r="P9" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -67401,7 +67852,7 @@
         <v>55.28</v>
       </c>
       <c r="I19" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="J19" t="s">
         <v>89</v>
@@ -67596,7 +68047,7 @@
         <v>736</v>
       </c>
       <c r="J23" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K23" t="s">
         <v>739</v>
@@ -67605,7 +68056,7 @@
         <v>386</v>
       </c>
       <c r="M23" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="N23" t="s">
         <v>295</v>
@@ -68697,7 +69148,7 @@
         <v>1.35</v>
       </c>
       <c r="I46" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="J46" t="s">
         <v>676</v>
@@ -68937,7 +69388,7 @@
         <v>5.74</v>
       </c>
       <c r="I51" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="J51" t="s">
         <v>89</v>
@@ -71196,7 +71647,7 @@
         <v>736</v>
       </c>
       <c r="J98" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K98" t="s">
         <v>739</v>
@@ -71205,7 +71656,7 @@
         <v>386</v>
       </c>
       <c r="M98" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="N98" t="s">
         <v>295</v>
@@ -71724,16 +72175,16 @@
         <v>59</v>
       </c>
       <c r="J109" t="s">
+        <v>939</v>
+      </c>
+      <c r="K109" t="s">
+        <v>940</v>
+      </c>
+      <c r="L109" t="s">
         <v>941</v>
       </c>
-      <c r="K109" t="s">
+      <c r="M109" t="s">
         <v>942</v>
-      </c>
-      <c r="L109" t="s">
-        <v>943</v>
-      </c>
-      <c r="M109" t="s">
-        <v>944</v>
       </c>
       <c r="N109" t="s">
         <v>64</v>
@@ -71961,7 +72412,7 @@
         <v>131.7</v>
       </c>
       <c r="I114" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="J114" t="s">
         <v>89</v>
@@ -72249,7 +72700,7 @@
         <v>10.14</v>
       </c>
       <c r="I120" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="J120" t="s">
         <v>269</v>
@@ -72261,7 +72712,7 @@
         <v>#N/A</v>
       </c>
       <c r="M120" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="N120" t="s">
         <v>101</v>
@@ -72444,7 +72895,7 @@
         <v>147</v>
       </c>
       <c r="J124" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="K124" t="s">
         <v>150</v>
@@ -72633,7 +73084,7 @@
         <v>3.94</v>
       </c>
       <c r="I128" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="J128" t="s">
         <v>754</v>
@@ -73068,16 +73519,16 @@
         <v>59</v>
       </c>
       <c r="J137" t="s">
+        <v>939</v>
+      </c>
+      <c r="K137" t="s">
+        <v>940</v>
+      </c>
+      <c r="L137" t="s">
         <v>941</v>
       </c>
-      <c r="K137" t="s">
+      <c r="M137" t="s">
         <v>942</v>
-      </c>
-      <c r="L137" t="s">
-        <v>943</v>
-      </c>
-      <c r="M137" t="s">
-        <v>944</v>
       </c>
       <c r="N137" t="s">
         <v>64</v>
@@ -74796,7 +75247,7 @@
         <v>575</v>
       </c>
       <c r="J173" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="K173" t="s">
         <v>578</v>
@@ -74805,7 +75256,7 @@
         <v>#N/A</v>
       </c>
       <c r="M173" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="N173" t="s">
         <v>152</v>
@@ -75129,7 +75580,7 @@
         <v>18.69</v>
       </c>
       <c r="I180" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="J180" t="s">
         <v>269</v>
@@ -75141,7 +75592,7 @@
         <v>#N/A</v>
       </c>
       <c r="M180" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="N180" t="s">
         <v>101</v>
@@ -75609,7 +76060,7 @@
         <v>156.66</v>
       </c>
       <c r="I190" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="J190" t="s">
         <v>89</v>
@@ -76233,7 +76684,7 @@
         <v>53.3</v>
       </c>
       <c r="I203" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="J203" t="s">
         <v>89</v>
@@ -76428,16 +76879,16 @@
         <v>59</v>
       </c>
       <c r="J207" t="s">
+        <v>939</v>
+      </c>
+      <c r="K207" t="s">
+        <v>940</v>
+      </c>
+      <c r="L207" t="s">
         <v>941</v>
       </c>
-      <c r="K207" t="s">
+      <c r="M207" t="s">
         <v>942</v>
-      </c>
-      <c r="L207" t="s">
-        <v>943</v>
-      </c>
-      <c r="M207" t="s">
-        <v>944</v>
       </c>
       <c r="N207" t="s">
         <v>64</v>
@@ -77196,7 +77647,7 @@
         <v>736</v>
       </c>
       <c r="J223" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K223" t="s">
         <v>739</v>
@@ -77205,7 +77656,7 @@
         <v>386</v>
       </c>
       <c r="M223" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="N223" t="s">
         <v>295</v>
@@ -77868,7 +78319,7 @@
         <v>736</v>
       </c>
       <c r="J237" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K237" t="s">
         <v>739</v>
@@ -77877,7 +78328,7 @@
         <v>386</v>
       </c>
       <c r="M237" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="N237" t="s">
         <v>295</v>
@@ -78444,7 +78895,7 @@
         <v>374</v>
       </c>
       <c r="J249" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K249" t="s">
         <v>377</v>
@@ -78489,7 +78940,7 @@
         <v>46.77</v>
       </c>
       <c r="I250" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="J250" t="s">
         <v>676</v>
@@ -78876,7 +79327,7 @@
         <v>736</v>
       </c>
       <c r="J258" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K258" t="s">
         <v>739</v>
@@ -78885,7 +79336,7 @@
         <v>386</v>
       </c>
       <c r="M258" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="N258" t="s">
         <v>295</v>
@@ -79596,7 +80047,7 @@
         <v>147</v>
       </c>
       <c r="J273" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="K273" t="s">
         <v>150</v>
@@ -80460,7 +80911,7 @@
         <v>575</v>
       </c>
       <c r="J291" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="K291" t="s">
         <v>578</v>
@@ -80469,7 +80920,7 @@
         <v>#N/A</v>
       </c>
       <c r="M291" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="N291" t="s">
         <v>152</v>
@@ -81468,16 +81919,16 @@
         <v>59</v>
       </c>
       <c r="J312" t="s">
+        <v>939</v>
+      </c>
+      <c r="K312" t="s">
+        <v>940</v>
+      </c>
+      <c r="L312" t="s">
         <v>941</v>
       </c>
-      <c r="K312" t="s">
+      <c r="M312" t="s">
         <v>942</v>
-      </c>
-      <c r="L312" t="s">
-        <v>943</v>
-      </c>
-      <c r="M312" t="s">
-        <v>944</v>
       </c>
       <c r="N312" t="s">
         <v>64</v>
@@ -81513,7 +81964,7 @@
         <v>8.05</v>
       </c>
       <c r="I313" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="J313" t="s">
         <v>89</v>
@@ -81849,7 +82300,7 @@
         <v>88.4</v>
       </c>
       <c r="I320" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="J320" t="s">
         <v>89</v>
@@ -81945,7 +82396,7 @@
         <v>6.54</v>
       </c>
       <c r="I322" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="J322" t="s">
         <v>269</v>
@@ -81957,7 +82408,7 @@
         <v>#N/A</v>
       </c>
       <c r="M322" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="N322" t="s">
         <v>101</v>
@@ -82713,7 +83164,7 @@
         <v>59.14</v>
       </c>
       <c r="I338" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="J338" t="s">
         <v>89</v>
@@ -83292,7 +83743,7 @@
         <v>736</v>
       </c>
       <c r="J350" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K350" t="s">
         <v>739</v>
@@ -83301,7 +83752,7 @@
         <v>386</v>
       </c>
       <c r="M350" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="N350" t="s">
         <v>295</v>
@@ -83769,7 +84220,7 @@
         <v>79.4</v>
       </c>
       <c r="I360" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="J360" t="s">
         <v>676</v>
@@ -84009,7 +84460,7 @@
         <v>80.65</v>
       </c>
       <c r="I365" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="J365" t="s">
         <v>754</v>
@@ -84444,7 +84895,7 @@
         <v>374</v>
       </c>
       <c r="J374" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K374" t="s">
         <v>377</v>
@@ -84825,7 +85276,7 @@
         <v>30.36</v>
       </c>
       <c r="I382" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="J382" t="s">
         <v>89</v>
@@ -86652,7 +87103,7 @@
         <v>575</v>
       </c>
       <c r="J420" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="K420" t="s">
         <v>578</v>
@@ -86661,7 +87112,7 @@
         <v>#N/A</v>
       </c>
       <c r="M420" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="N420" t="s">
         <v>152</v>
@@ -87273,7 +87724,7 @@
         <v>27.94</v>
       </c>
       <c r="I433" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="J433" t="s">
         <v>89</v>
@@ -87897,7 +88348,7 @@
         <v>61.02</v>
       </c>
       <c r="I446" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="J446" t="s">
         <v>36</v>
@@ -87948,7 +88399,7 @@
         <v>736</v>
       </c>
       <c r="J447" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K447" t="s">
         <v>739</v>
@@ -87957,7 +88408,7 @@
         <v>386</v>
       </c>
       <c r="M447" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="N447" t="s">
         <v>295</v>
@@ -88092,7 +88543,7 @@
         <v>736</v>
       </c>
       <c r="J450" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K450" t="s">
         <v>739</v>
@@ -88101,7 +88552,7 @@
         <v>386</v>
       </c>
       <c r="M450" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="N450" t="s">
         <v>295</v>
@@ -88377,7 +88828,7 @@
         <v>23.94</v>
       </c>
       <c r="I456" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="J456" t="s">
         <v>36</v>
@@ -88620,16 +89071,16 @@
         <v>59</v>
       </c>
       <c r="J461" t="s">
+        <v>939</v>
+      </c>
+      <c r="K461" t="s">
+        <v>940</v>
+      </c>
+      <c r="L461" t="s">
         <v>941</v>
       </c>
-      <c r="K461" t="s">
+      <c r="M461" t="s">
         <v>942</v>
-      </c>
-      <c r="L461" t="s">
-        <v>943</v>
-      </c>
-      <c r="M461" t="s">
-        <v>944</v>
       </c>
       <c r="N461" t="s">
         <v>64</v>
@@ -89388,7 +89839,7 @@
         <v>736</v>
       </c>
       <c r="J477" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K477" t="s">
         <v>739</v>
@@ -89397,7 +89848,7 @@
         <v>386</v>
       </c>
       <c r="M477" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="N477" t="s">
         <v>295</v>
@@ -89772,7 +90223,7 @@
         <v>147</v>
       </c>
       <c r="J485" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="K485" t="s">
         <v>150</v>
@@ -90204,7 +90655,7 @@
         <v>736</v>
       </c>
       <c r="J494" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K494" t="s">
         <v>739</v>
@@ -90213,7 +90664,7 @@
         <v>386</v>
       </c>
       <c r="M494" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="N494" t="s">
         <v>295</v>
@@ -90252,16 +90703,16 @@
         <v>59</v>
       </c>
       <c r="J495" t="s">
+        <v>939</v>
+      </c>
+      <c r="K495" t="s">
+        <v>940</v>
+      </c>
+      <c r="L495" t="s">
         <v>941</v>
       </c>
-      <c r="K495" t="s">
+      <c r="M495" t="s">
         <v>942</v>
-      </c>
-      <c r="L495" t="s">
-        <v>943</v>
-      </c>
-      <c r="M495" t="s">
-        <v>944</v>
       </c>
       <c r="N495" t="s">
         <v>64</v>
@@ -90348,16 +90799,16 @@
         <v>59</v>
       </c>
       <c r="J497" t="s">
+        <v>939</v>
+      </c>
+      <c r="K497" t="s">
+        <v>940</v>
+      </c>
+      <c r="L497" t="s">
         <v>941</v>
       </c>
-      <c r="K497" t="s">
+      <c r="M497" t="s">
         <v>942</v>
-      </c>
-      <c r="L497" t="s">
-        <v>943</v>
-      </c>
-      <c r="M497" t="s">
-        <v>944</v>
       </c>
       <c r="N497" t="s">
         <v>64</v>
@@ -90492,7 +90943,7 @@
         <v>147</v>
       </c>
       <c r="J500" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="K500" t="s">
         <v>150</v>
@@ -90732,7 +91183,7 @@
         <v>575</v>
       </c>
       <c r="J505" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="K505" t="s">
         <v>578</v>
@@ -90741,7 +91192,7 @@
         <v>#N/A</v>
       </c>
       <c r="M505" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="N505" t="s">
         <v>152</v>
@@ -91068,7 +91519,7 @@
         <v>575</v>
       </c>
       <c r="J512" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="K512" t="s">
         <v>578</v>
@@ -91077,7 +91528,7 @@
         <v>#N/A</v>
       </c>
       <c r="M512" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="N512" t="s">
         <v>152</v>
@@ -91548,16 +91999,16 @@
         <v>59</v>
       </c>
       <c r="J522" t="s">
+        <v>939</v>
+      </c>
+      <c r="K522" t="s">
+        <v>940</v>
+      </c>
+      <c r="L522" t="s">
         <v>941</v>
       </c>
-      <c r="K522" t="s">
+      <c r="M522" t="s">
         <v>942</v>
-      </c>
-      <c r="L522" t="s">
-        <v>943</v>
-      </c>
-      <c r="M522" t="s">
-        <v>944</v>
       </c>
       <c r="N522" t="s">
         <v>64</v>
@@ -92697,7 +93148,7 @@
         <v>23.79</v>
       </c>
       <c r="I546" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="J546" t="s">
         <v>754</v>
@@ -92748,16 +93199,16 @@
         <v>59</v>
       </c>
       <c r="J547" t="s">
+        <v>939</v>
+      </c>
+      <c r="K547" t="s">
+        <v>940</v>
+      </c>
+      <c r="L547" t="s">
         <v>941</v>
       </c>
-      <c r="K547" t="s">
+      <c r="M547" t="s">
         <v>942</v>
-      </c>
-      <c r="L547" t="s">
-        <v>943</v>
-      </c>
-      <c r="M547" t="s">
-        <v>944</v>
       </c>
       <c r="N547" t="s">
         <v>64</v>
@@ -93564,7 +94015,7 @@
         <v>374</v>
       </c>
       <c r="J564" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K564" t="s">
         <v>377</v>
@@ -94329,7 +94780,7 @@
         <v>7.09</v>
       </c>
       <c r="I580" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="J580" t="s">
         <v>89</v>
@@ -94521,7 +94972,7 @@
         <v>81.83</v>
       </c>
       <c r="I584" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="J584" t="s">
         <v>676</v>
@@ -94713,7 +95164,7 @@
         <v>29.78</v>
       </c>
       <c r="I588" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="J588" t="s">
         <v>676</v>
@@ -94761,7 +95212,7 @@
         <v>69.53</v>
       </c>
       <c r="I589" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="J589" t="s">
         <v>36</v>
@@ -94953,7 +95404,7 @@
         <v>35.43</v>
       </c>
       <c r="I593" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="J593" t="s">
         <v>676</v>
@@ -96012,7 +96463,7 @@
         <v>736</v>
       </c>
       <c r="J615" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K615" t="s">
         <v>739</v>
@@ -96021,7 +96472,7 @@
         <v>386</v>
       </c>
       <c r="M615" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="N615" t="s">
         <v>295</v>
@@ -96156,16 +96607,16 @@
         <v>59</v>
       </c>
       <c r="J618" t="s">
+        <v>939</v>
+      </c>
+      <c r="K618" t="s">
+        <v>940</v>
+      </c>
+      <c r="L618" t="s">
         <v>941</v>
       </c>
-      <c r="K618" t="s">
+      <c r="M618" t="s">
         <v>942</v>
-      </c>
-      <c r="L618" t="s">
-        <v>943</v>
-      </c>
-      <c r="M618" t="s">
-        <v>944</v>
       </c>
       <c r="N618" t="s">
         <v>64</v>
@@ -96441,7 +96892,7 @@
         <v>12.04</v>
       </c>
       <c r="I624" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="J624" t="s">
         <v>754</v>
@@ -97257,7 +97708,7 @@
         <v>1.25</v>
       </c>
       <c r="I641" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="J641" t="s">
         <v>269</v>
@@ -97269,7 +97720,7 @@
         <v>#N/A</v>
       </c>
       <c r="M641" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="N641" t="s">
         <v>101</v>
@@ -98076,7 +98527,7 @@
         <v>736</v>
       </c>
       <c r="J658" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K658" t="s">
         <v>739</v>
@@ -98085,7 +98536,7 @@
         <v>386</v>
       </c>
       <c r="M658" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="N658" t="s">
         <v>295</v>
@@ -98169,7 +98620,7 @@
         <v>26.29</v>
       </c>
       <c r="I660" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="J660" t="s">
         <v>754</v>
@@ -98844,16 +99295,16 @@
         <v>59</v>
       </c>
       <c r="J674" t="s">
+        <v>939</v>
+      </c>
+      <c r="K674" t="s">
+        <v>940</v>
+      </c>
+      <c r="L674" t="s">
         <v>941</v>
       </c>
-      <c r="K674" t="s">
+      <c r="M674" t="s">
         <v>942</v>
-      </c>
-      <c r="L674" t="s">
-        <v>943</v>
-      </c>
-      <c r="M674" t="s">
-        <v>944</v>
       </c>
       <c r="N674" t="s">
         <v>64</v>
@@ -99225,7 +99676,7 @@
         <v>1.36</v>
       </c>
       <c r="I682" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="J682" t="s">
         <v>269</v>
@@ -99237,7 +99688,7 @@
         <v>#N/A</v>
       </c>
       <c r="M682" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="N682" t="s">
         <v>101</v>
@@ -99372,7 +99823,7 @@
         <v>575</v>
       </c>
       <c r="J685" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="K685" t="s">
         <v>578</v>
@@ -99381,7 +99832,7 @@
         <v>#N/A</v>
       </c>
       <c r="M685" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="N685" t="s">
         <v>152</v>
@@ -100332,7 +100783,7 @@
         <v>575</v>
       </c>
       <c r="J705" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="K705" t="s">
         <v>578</v>
@@ -100341,7 +100792,7 @@
         <v>#N/A</v>
       </c>
       <c r="M705" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="N705" t="s">
         <v>152</v>
@@ -100377,7 +100828,7 @@
         <v>40.42</v>
       </c>
       <c r="I706" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="J706" t="s">
         <v>36</v>
@@ -100428,16 +100879,16 @@
         <v>59</v>
       </c>
       <c r="J707" t="s">
+        <v>939</v>
+      </c>
+      <c r="K707" t="s">
+        <v>940</v>
+      </c>
+      <c r="L707" t="s">
         <v>941</v>
       </c>
-      <c r="K707" t="s">
+      <c r="M707" t="s">
         <v>942</v>
-      </c>
-      <c r="L707" t="s">
-        <v>943</v>
-      </c>
-      <c r="M707" t="s">
-        <v>944</v>
       </c>
       <c r="N707" t="s">
         <v>64</v>
@@ -101052,7 +101503,7 @@
         <v>147</v>
       </c>
       <c r="J720" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="K720" t="s">
         <v>150</v>
@@ -102585,7 +103036,7 @@
         <v>20.31</v>
       </c>
       <c r="I752" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="J752" t="s">
         <v>754</v>
@@ -103209,7 +103660,7 @@
         <v>1.21</v>
       </c>
       <c r="I765" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="J765" t="s">
         <v>36</v>
@@ -103452,16 +103903,16 @@
         <v>59</v>
       </c>
       <c r="J770" t="s">
+        <v>939</v>
+      </c>
+      <c r="K770" t="s">
+        <v>940</v>
+      </c>
+      <c r="L770" t="s">
         <v>941</v>
       </c>
-      <c r="K770" t="s">
+      <c r="M770" t="s">
         <v>942</v>
-      </c>
-      <c r="L770" t="s">
-        <v>943</v>
-      </c>
-      <c r="M770" t="s">
-        <v>944</v>
       </c>
       <c r="N770" t="s">
         <v>64</v>
@@ -104076,7 +104527,7 @@
         <v>147</v>
       </c>
       <c r="J783" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="K783" t="s">
         <v>150</v>
@@ -104220,7 +104671,7 @@
         <v>736</v>
       </c>
       <c r="J786" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K786" t="s">
         <v>739</v>
@@ -104229,7 +104680,7 @@
         <v>386</v>
       </c>
       <c r="M786" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="N786" t="s">
         <v>295</v>
@@ -104268,7 +104719,7 @@
         <v>575</v>
       </c>
       <c r="J787" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="K787" t="s">
         <v>578</v>
@@ -104277,7 +104728,7 @@
         <v>#N/A</v>
       </c>
       <c r="M787" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="N787" t="s">
         <v>152</v>
@@ -104652,7 +105103,7 @@
         <v>147</v>
       </c>
       <c r="J795" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="K795" t="s">
         <v>150</v>
@@ -104793,7 +105244,7 @@
         <v>8.72</v>
       </c>
       <c r="I798" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="J798" t="s">
         <v>754</v>
@@ -105852,7 +106303,7 @@
         <v>736</v>
       </c>
       <c r="J820" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="K820" t="s">
         <v>739</v>
@@ -105861,7 +106312,7 @@
         <v>386</v>
       </c>
       <c r="M820" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="N820" t="s">
         <v>295</v>
@@ -106284,7 +106735,7 @@
         <v>575</v>
       </c>
       <c r="J829" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="K829" t="s">
         <v>578</v>
@@ -106293,7 +106744,7 @@
         <v>#N/A</v>
       </c>
       <c r="M829" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="N829" t="s">
         <v>152</v>
@@ -106408,47 +106859,50 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B1" t="s">
+        <v>948</v>
+      </c>
+      <c r="C1" t="s">
+        <v>949</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
         <v>950</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
+        <v>897</v>
+      </c>
+      <c r="G1" t="s">
         <v>951</v>
       </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>952</v>
       </c>
-      <c r="F1" t="s">
-        <v>899</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>953</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>954</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>955</v>
       </c>
-      <c r="J1" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="C2">
         <v>8</v>
@@ -106457,7 +106911,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F2">
         <v>18</v>
@@ -106475,12 +106929,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -106489,7 +106943,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F3">
         <v>19</v>
@@ -106506,13 +106960,16 @@
       <c r="J3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -106521,7 +106978,7 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -106539,12 +106996,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -106553,7 +107010,7 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F5">
         <v>22</v>
@@ -106571,12 +107028,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -106585,7 +107042,7 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F6">
         <v>21.35</v>
@@ -106603,12 +107060,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -106617,7 +107074,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F7">
         <v>25</v>
@@ -106635,12 +107092,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -106649,7 +107106,7 @@
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F8">
         <v>30</v>
@@ -106667,12 +107124,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -106681,7 +107138,7 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F9">
         <v>40</v>
@@ -106699,12 +107156,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -106713,7 +107170,7 @@
         <v>6</v>
       </c>
       <c r="E10" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F10">
         <v>97</v>
@@ -106731,12 +107188,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -106745,7 +107202,7 @@
         <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="F11">
         <v>31</v>
@@ -106763,12 +107220,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -106777,7 +107234,7 @@
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F12">
         <v>21</v>
@@ -106795,12 +107252,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -106809,7 +107266,7 @@
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F13">
         <v>38</v>
@@ -106827,12 +107284,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C14">
         <v>6</v>
@@ -106841,7 +107298,7 @@
         <v>8</v>
       </c>
       <c r="E14" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F14">
         <v>6</v>
@@ -106859,12 +107316,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -106873,7 +107330,7 @@
         <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F15">
         <v>23.25</v>
@@ -106891,12 +107348,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -106905,7 +107362,7 @@
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F16">
         <v>13</v>
@@ -106928,7 +107385,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -106937,7 +107394,7 @@
         <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F17">
         <v>17.45</v>
@@ -106960,7 +107417,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="C18">
         <v>7</v>
@@ -106969,7 +107426,7 @@
         <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F18">
         <v>39</v>
@@ -106992,7 +107449,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="C19">
         <v>7</v>
@@ -107001,7 +107458,7 @@
         <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F19">
         <v>62.5</v>
@@ -107024,7 +107481,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -107033,7 +107490,7 @@
         <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="F20">
         <v>9.2</v>
@@ -107056,7 +107513,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C21">
         <v>8</v>
@@ -107065,7 +107522,7 @@
         <v>3</v>
       </c>
       <c r="E21" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F21">
         <v>81</v>
@@ -107088,7 +107545,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="C22">
         <v>8</v>
@@ -107097,7 +107554,7 @@
         <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F22">
         <v>10</v>
@@ -107120,7 +107577,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="C23">
         <v>9</v>
@@ -107129,7 +107586,7 @@
         <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F23">
         <v>21</v>
@@ -107152,7 +107609,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="C24">
         <v>9</v>
@@ -107161,7 +107618,7 @@
         <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F24">
         <v>9</v>
@@ -107184,7 +107641,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="C25">
         <v>10</v>
@@ -107193,7 +107650,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F25">
         <v>4.5</v>
@@ -107216,7 +107673,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C26">
         <v>11</v>
@@ -107225,7 +107682,7 @@
         <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="F26">
         <v>14</v>
@@ -107248,7 +107705,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="C27">
         <v>11</v>
@@ -107257,7 +107714,7 @@
         <v>3</v>
       </c>
       <c r="E27" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="F27">
         <v>31.23</v>
@@ -107280,7 +107737,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="C28">
         <v>11</v>
@@ -107289,7 +107746,7 @@
         <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="F28">
         <v>43.9</v>
@@ -107312,7 +107769,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C29">
         <v>12</v>
@@ -107321,7 +107778,7 @@
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="F29">
         <v>45.6</v>
@@ -107344,7 +107801,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="C30">
         <v>12</v>
@@ -107353,7 +107810,7 @@
         <v>6</v>
       </c>
       <c r="E30" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F30">
         <v>123.79</v>
@@ -107376,7 +107833,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C31">
         <v>13</v>
@@ -107385,7 +107842,7 @@
         <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="F31">
         <v>25.89</v>
@@ -107408,7 +107865,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C32">
         <v>14</v>
@@ -107417,7 +107874,7 @@
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="F32">
         <v>12.5</v>
@@ -107440,7 +107897,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C33">
         <v>14</v>
@@ -107449,7 +107906,7 @@
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F33">
         <v>32</v>
@@ -107472,7 +107929,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C34">
         <v>15</v>
@@ -107481,7 +107938,7 @@
         <v>4</v>
       </c>
       <c r="E34" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="F34">
         <v>2.5</v>
@@ -107504,7 +107961,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C35">
         <v>16</v>
@@ -107513,7 +107970,7 @@
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F35">
         <v>14</v>
@@ -107536,7 +107993,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C36">
         <v>16</v>
@@ -107545,7 +108002,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F36">
         <v>18</v>
@@ -107568,7 +108025,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C37">
         <v>17</v>
@@ -107577,7 +108034,7 @@
         <v>8</v>
       </c>
       <c r="E37" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="F37">
         <v>19</v>
@@ -107600,7 +108057,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C38">
         <v>17</v>
@@ -107609,7 +108066,7 @@
         <v>8</v>
       </c>
       <c r="E38" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="F38">
         <v>26</v>
@@ -107632,7 +108089,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C39">
         <v>18</v>
@@ -107641,7 +108098,7 @@
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="F39">
         <v>263.5</v>
@@ -107664,7 +108121,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C40">
         <v>18</v>
@@ -107673,7 +108130,7 @@
         <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="F40">
         <v>18</v>
@@ -107696,7 +108153,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="C41">
         <v>19</v>
@@ -107705,7 +108162,7 @@
         <v>8</v>
       </c>
       <c r="E41" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="F41">
         <v>18.4</v>
@@ -107728,7 +108185,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C42">
         <v>19</v>
@@ -107737,7 +108194,7 @@
         <v>8</v>
       </c>
       <c r="E42" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="F42">
         <v>9.65</v>
@@ -107760,7 +108217,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C43">
         <v>20</v>
@@ -107769,7 +108226,7 @@
         <v>5</v>
       </c>
       <c r="E43" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F43">
         <v>14</v>
@@ -107792,7 +108249,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C44">
         <v>20</v>
@@ -107801,7 +108258,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F44">
         <v>46</v>
@@ -107824,7 +108281,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C45">
         <v>20</v>
@@ -107833,7 +108290,7 @@
         <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F45">
         <v>19.45</v>
@@ -107856,7 +108313,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C46">
         <v>21</v>
@@ -107865,7 +108322,7 @@
         <v>8</v>
       </c>
       <c r="E46" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F46">
         <v>9.5</v>
@@ -107888,7 +108345,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C47">
         <v>21</v>
@@ -107897,7 +108354,7 @@
         <v>8</v>
       </c>
       <c r="E47" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F47">
         <v>12</v>
@@ -107920,7 +108377,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C48">
         <v>22</v>
@@ -107929,7 +108386,7 @@
         <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F48">
         <v>9.5</v>
@@ -107952,7 +108409,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C49">
         <v>22</v>
@@ -107961,7 +108418,7 @@
         <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F49">
         <v>12.75</v>
@@ -107984,7 +108441,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C50">
         <v>23</v>
@@ -107993,7 +108450,7 @@
         <v>3</v>
       </c>
       <c r="E50" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F50">
         <v>20</v>
@@ -108016,7 +108473,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C51">
         <v>23</v>
@@ -108025,7 +108482,7 @@
         <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F51">
         <v>16.25</v>
@@ -108048,7 +108505,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C52">
         <v>24</v>
@@ -108057,7 +108514,7 @@
         <v>7</v>
       </c>
       <c r="E52" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F52">
         <v>53</v>
@@ -108080,7 +108537,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C53">
         <v>24</v>
@@ -108089,7 +108546,7 @@
         <v>5</v>
       </c>
       <c r="E53" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F53">
         <v>7</v>
@@ -108112,7 +108569,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C54">
         <v>24</v>
@@ -108121,7 +108578,7 @@
         <v>6</v>
       </c>
       <c r="E54" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F54">
         <v>32.8</v>
@@ -108144,7 +108601,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C55">
         <v>25</v>
@@ -108153,7 +108610,7 @@
         <v>6</v>
       </c>
       <c r="E55" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="F55">
         <v>7.45</v>
@@ -108176,7 +108633,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C56">
         <v>25</v>
@@ -108185,7 +108642,7 @@
         <v>6</v>
       </c>
       <c r="E56" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F56">
         <v>24</v>
@@ -108208,7 +108665,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C57">
         <v>26</v>
@@ -108217,7 +108674,7 @@
         <v>5</v>
       </c>
       <c r="E57" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F57">
         <v>38</v>
@@ -108240,7 +108697,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C58">
         <v>26</v>
@@ -108249,7 +108706,7 @@
         <v>5</v>
       </c>
       <c r="E58" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F58">
         <v>19.5</v>
@@ -108272,7 +108729,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C59">
         <v>27</v>
@@ -108281,7 +108738,7 @@
         <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="F59">
         <v>13.25</v>
@@ -108304,7 +108761,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C60">
         <v>28</v>
@@ -108313,7 +108770,7 @@
         <v>4</v>
       </c>
       <c r="E60" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="F60">
         <v>55</v>
@@ -108336,7 +108793,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C61">
         <v>28</v>
@@ -108345,7 +108802,7 @@
         <v>4</v>
       </c>
       <c r="E61" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="F61">
         <v>34</v>
@@ -108368,7 +108825,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C62">
         <v>29</v>
@@ -108377,7 +108834,7 @@
         <v>2</v>
       </c>
       <c r="E62" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F62">
         <v>28.5</v>
@@ -108400,7 +108857,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C63">
         <v>29</v>
@@ -108409,7 +108866,7 @@
         <v>3</v>
       </c>
       <c r="E63" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F63">
         <v>49.3</v>
@@ -108432,7 +108889,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C64">
         <v>7</v>
@@ -108441,7 +108898,7 @@
         <v>2</v>
       </c>
       <c r="E64" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="F64">
         <v>43.9</v>
@@ -108464,7 +108921,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C65">
         <v>12</v>
@@ -108473,7 +108930,7 @@
         <v>5</v>
       </c>
       <c r="E65" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F65">
         <v>33.25</v>
@@ -108496,7 +108953,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C66">
         <v>2</v>
@@ -108505,7 +108962,7 @@
         <v>2</v>
       </c>
       <c r="E66" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F66">
         <v>21.05</v>
@@ -108528,7 +108985,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C67">
         <v>2</v>
@@ -108537,7 +108994,7 @@
         <v>2</v>
       </c>
       <c r="E67" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="F67">
         <v>17</v>
@@ -108560,7 +109017,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C68">
         <v>16</v>
@@ -108569,7 +109026,7 @@
         <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F68">
         <v>14</v>
@@ -108592,7 +109049,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="C69">
         <v>8</v>
@@ -108601,7 +109058,7 @@
         <v>3</v>
       </c>
       <c r="E69" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="F69">
         <v>12.5</v>
@@ -108624,7 +109081,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C70">
         <v>15</v>
@@ -108633,7 +109090,7 @@
         <v>4</v>
       </c>
       <c r="E70" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="F70">
         <v>36</v>
@@ -108656,7 +109113,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C71">
         <v>7</v>
@@ -108665,7 +109122,7 @@
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="F71">
         <v>15</v>
@@ -108688,7 +109145,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C72">
         <v>15</v>
@@ -108697,7 +109154,7 @@
         <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F72">
         <v>21.5</v>
@@ -108720,7 +109177,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C73">
         <v>14</v>
@@ -108729,7 +109186,7 @@
         <v>4</v>
       </c>
       <c r="E73" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F73">
         <v>34.8</v>
@@ -108752,7 +109209,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C74">
         <v>17</v>
@@ -108761,7 +109218,7 @@
         <v>8</v>
       </c>
       <c r="E74" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="F74">
         <v>15</v>
@@ -108784,7 +109241,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C75">
         <v>4</v>
@@ -108793,7 +109250,7 @@
         <v>7</v>
       </c>
       <c r="E75" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="F75">
         <v>10</v>
@@ -108816,7 +109273,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="C76">
         <v>12</v>
@@ -108825,7 +109282,7 @@
         <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F76">
         <v>7.75</v>
@@ -108848,7 +109305,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C77">
         <v>23</v>
@@ -108857,7 +109314,7 @@
         <v>1</v>
       </c>
       <c r="E77" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="F77">
         <v>18</v>
@@ -108880,7 +109337,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C78">
         <v>12</v>
@@ -108889,7 +109346,7 @@
         <v>2</v>
       </c>
       <c r="E78" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="F78">
         <v>13</v>
@@ -108908,6 +109365,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please select value from dropdown" promptTitle="Info" prompt="Seelect Category Name" sqref="K3:K31">
+      <formula1>categories!$B$2:$B$9</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
@@ -108921,10 +109383,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B1" t="s">
         <v>1104</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -108932,7 +109394,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -108940,7 +109402,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -108948,7 +109410,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -108956,7 +109418,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
   </sheetData>
@@ -108973,7 +109435,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B1" t="s">
         <v>22</v>
@@ -108987,10 +109449,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C2" t="s">
         <v>1111</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -108998,10 +109460,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C3" t="s">
         <v>1113</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -109009,10 +109471,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C4" t="s">
         <v>1115</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -109020,10 +109482,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C5" t="s">
         <v>1117</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -109031,10 +109493,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C6" t="s">
         <v>1119</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -109042,10 +109504,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C7" t="s">
         <v>1121</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1122</v>
       </c>
     </row>
   </sheetData>

--- a/June/21.06.2026/northwind.xlsx
+++ b/June/21.06.2026/northwind.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17760" windowHeight="12380" firstSheet="6" activeTab="13"/>
+    <workbookView windowHeight="17160" firstSheet="6" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="categories" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7231" uniqueCount="1499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7232" uniqueCount="1500">
   <si>
     <t>categoryid</t>
   </si>
@@ -4540,6 +4540,9 @@
   </si>
   <si>
     <t>Santosh</t>
+  </si>
+  <si>
+    <t>Sum</t>
   </si>
 </sst>
 </file>
@@ -8209,7 +8212,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="11.71875" customWidth="1"/>
@@ -8553,6 +8556,23 @@
       <c r="I11">
         <f t="shared" si="1"/>
         <v>51.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="B12" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C12">
+        <f>SUM(C2:C11)</f>
+        <v>587</v>
+      </c>
+      <c r="H12">
+        <f>SUM(H2:H11)</f>
+        <v>3282</v>
+      </c>
+      <c r="I12">
+        <f>SUM(I2:I11)</f>
+        <v>656.4</v>
       </c>
     </row>
   </sheetData>
